--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487618_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487618_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.8555</v>
+        <v>4.4349</v>
       </c>
       <c r="E2" t="n">
-        <v>5.2831</v>
+        <v>5.9443</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.4276</v>
+        <v>-1.5094</v>
       </c>
       <c r="G2" t="n">
         <v>4.5988</v>
@@ -610,13 +610,13 @@
         <v>2.7164</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2373</v>
+        <v>0.3421</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9567</v>
+        <v>-0.2956</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7194</v>
+        <v>0.6377</v>
       </c>
       <c r="V2" t="n">
         <v>-0.894</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5227</v>
+        <v>2.8653</v>
       </c>
       <c r="E3" t="n">
-        <v>3.4646</v>
+        <v>3.325</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0581</v>
+        <v>-0.4597</v>
       </c>
       <c r="G3" t="n">
         <v>0.8653999999999999</v>
@@ -688,13 +688,13 @@
         <v>1.9403</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9872</v>
+        <v>0.3298</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0134</v>
+        <v>-0.1262</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9738</v>
+        <v>0.456</v>
       </c>
       <c r="V3" t="n">
         <v>0.894</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8648</v>
+        <v>2.7801</v>
       </c>
       <c r="E4" t="n">
-        <v>3.3983</v>
+        <v>3.9593</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.5335</v>
+        <v>-1.1792</v>
       </c>
       <c r="G4" t="n">
         <v>3.6328</v>
@@ -766,13 +766,13 @@
         <v>2.3284</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6487000000000001</v>
+        <v>0.2667</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.0173</v>
+        <v>-0.4562</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3686</v>
+        <v>0.7229</v>
       </c>
       <c r="V4" t="n">
         <v>-3.0597</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.604</v>
+        <v>2.1194</v>
       </c>
       <c r="E5" t="n">
-        <v>3.6063</v>
+        <v>4.0673</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.0024</v>
+        <v>-1.9479</v>
       </c>
       <c r="G5" t="n">
         <v>4.7441</v>
@@ -844,13 +844,13 @@
         <v>1.7463</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5581</v>
+        <v>-0.0426</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6662</v>
+        <v>-0.2053</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1081</v>
+        <v>0.1626</v>
       </c>
       <c r="V5" t="n">
         <v>-1.2239</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. SAEZ BENITO</t>
+          <t>S. RODRIGUEZ GREGORIO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5859</v>
+        <v>0.1298</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2305</v>
+        <v>-1.0821</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8164</v>
+        <v>1.2119</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.6868</v>
+        <v>-0.7267</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.188</v>
+        <v>-0.4136</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4988</v>
+        <v>-0.3131</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.3188</v>
+        <v>0.2935</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.6919999999999999</v>
+        <v>0.1895</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6267</v>
+        <v>0.104</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3681</v>
+        <v>-1.0202</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.496</v>
+        <v>-0.6031</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1279</v>
+        <v>-0.4171</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.9702</v>
+        <v>0.5821</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9403</v>
+        <v>-1.3582</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9702</v>
+        <v>1.9403</v>
       </c>
       <c r="S6" t="n">
-        <v>1.4071</v>
+        <v>0.2266</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9107</v>
+        <v>-0.0174</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4964</v>
+        <v>0.244</v>
       </c>
       <c r="V6" t="n">
-        <v>1.8358</v>
+        <v>0.0478</v>
       </c>
       <c r="W6" t="n">
-        <v>2.1179</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2821</v>
+        <v>0.0478</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. RODRIGUEZ GREGORIO</t>
+          <t>J. SAEZ BENITO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4057</v>
+        <v>-0.0692</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9425</v>
+        <v>-0.8310999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3481</v>
+        <v>0.7619</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.7267</v>
+        <v>-1.6868</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4136</v>
+        <v>-1.188</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3131</v>
+        <v>-0.4988</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2935</v>
+        <v>-1.3188</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1895</v>
+        <v>-0.6919999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>0.104</v>
+        <v>-0.6267</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.0202</v>
+        <v>-0.3681</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6031</v>
+        <v>-0.496</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4171</v>
+        <v>0.1279</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5821</v>
+        <v>-0.9702</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.3582</v>
+        <v>-1.9403</v>
       </c>
       <c r="R7" t="n">
-        <v>1.9403</v>
+        <v>0.9702</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5024999999999999</v>
+        <v>0.752</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1222</v>
+        <v>0.3101</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3802</v>
+        <v>0.4419</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0478</v>
+        <v>1.8358</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.1179</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0478</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. TOLOSA OROPESA</t>
+          <t>L. BERMEJO ALCALDE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3077</v>
+        <v>-0.5901999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4489</v>
+        <v>0.3757</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1412</v>
+        <v>-0.9658</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.5141</v>
+        <v>1.2669</v>
       </c>
       <c r="H8" t="n">
-        <v>1.9979</v>
+        <v>0.3905</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.512</v>
+        <v>0.8764</v>
       </c>
       <c r="J8" t="n">
-        <v>0.399</v>
+        <v>2.3537</v>
       </c>
       <c r="K8" t="n">
-        <v>2.3604</v>
+        <v>1.0546</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.9614</v>
+        <v>1.2991</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.9131</v>
+        <v>-1.0867</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3625</v>
+        <v>-0.6641</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5506</v>
+        <v>-0.4227</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.5821</v>
+        <v>-0.7761</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1642</v>
+        <v>-2.1344</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5821</v>
+        <v>1.3582</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7885</v>
+        <v>-0.0914</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3163</v>
+        <v>-0.078</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4722</v>
+        <v>-0.0134</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.9896</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.2343</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>L. BERMEJO ALCALDE</t>
+          <t>D. TOLOSA OROPESA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.499</v>
+        <v>-0.7081</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5759</v>
+        <v>-0.8493000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.0748</v>
+        <v>0.1412</v>
       </c>
       <c r="G9" t="n">
-        <v>1.2669</v>
+        <v>-0.5141</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3905</v>
+        <v>1.9979</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8764</v>
+        <v>-2.512</v>
       </c>
       <c r="J9" t="n">
-        <v>2.3537</v>
+        <v>0.399</v>
       </c>
       <c r="K9" t="n">
-        <v>1.0546</v>
+        <v>2.3604</v>
       </c>
       <c r="L9" t="n">
-        <v>1.2991</v>
+        <v>-1.9614</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.0867</v>
+        <v>-0.9131</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6641</v>
+        <v>-0.3625</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4227</v>
+        <v>-0.5506</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.7761</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.1344</v>
+        <v>-1.1642</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3582</v>
+        <v>0.5821</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0002</v>
+        <v>0.3881</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1222</v>
+        <v>-0.08409999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1225</v>
+        <v>0.4722</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.9896</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2343</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.7893</v>
+        <v>-1.6347</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.5842</v>
+        <v>-1.4841</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.205</v>
+        <v>-0.1505</v>
       </c>
       <c r="G10" t="n">
         <v>-0.3936</v>
@@ -1234,13 +1234,13 @@
         <v>0.3881</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.09710000000000001</v>
+        <v>0.0575</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>0.1001</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.09710000000000001</v>
+        <v>-0.0426</v>
       </c>
       <c r="V10" t="n">
         <v>1.2239</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.832</v>
+        <v>-2.1962</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.3891</v>
+        <v>-0.8895999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4429</v>
+        <v>-1.3066</v>
       </c>
       <c r="G11" t="n">
         <v>-3.3276</v>
@@ -1312,13 +1312,13 @@
         <v>1.1642</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6135</v>
+        <v>0.2493</v>
       </c>
       <c r="T11" t="n">
-        <v>0.7896</v>
+        <v>0.2891</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1761</v>
+        <v>-0.0398</v>
       </c>
       <c r="V11" t="n">
         <v>-0.2821</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.1958</v>
+        <v>-2.6135</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.4621</v>
+        <v>-0.9616</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.7337</v>
+        <v>-1.6519</v>
       </c>
       <c r="G12" t="n">
         <v>-3.3379</v>
@@ -1390,13 +1390,13 @@
         <v>1.3582</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5758</v>
+        <v>0.0064</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5933</v>
+        <v>-0.09279999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0175</v>
+        <v>0.0993</v>
       </c>
       <c r="V12" t="n">
         <v>0.3299</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.214799999999999</v>
+        <v>4.517599999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>11.2709</v>
+        <v>11.5738</v>
       </c>
       <c r="F13" t="n">
-        <v>-7.0561</v>
+        <v>-7.055999999999999</v>
       </c>
       <c r="G13" t="n">
         <v>5.121300000000002</v>
@@ -1468,13 +1468,13 @@
         <v>16.4927</v>
       </c>
       <c r="S13" t="n">
-        <v>2.1816</v>
+        <v>2.4845</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9591000000000003</v>
+        <v>-0.6563</v>
       </c>
       <c r="U13" t="n">
-        <v>3.1405</v>
+        <v>3.1408</v>
       </c>
       <c r="V13" t="n">
         <v>-2.1179</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.3882</v>
+        <v>5.1584</v>
       </c>
       <c r="E14" t="n">
-        <v>5.4986</v>
+        <v>5.9991</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.1104</v>
+        <v>-0.8406</v>
       </c>
       <c r="G14" t="n">
         <v>3.4501</v>
@@ -1546,13 +1546,13 @@
         <v>2.7164</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.3156</v>
+        <v>-0.5454</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.1384</v>
+        <v>-0.6379</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1772</v>
+        <v>0.0926</v>
       </c>
       <c r="V14" t="n">
         <v>2.4477</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.0176</v>
+        <v>4.5449</v>
       </c>
       <c r="E15" t="n">
-        <v>4.6009</v>
+        <v>4.8011</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.5833</v>
+        <v>-0.2562</v>
       </c>
       <c r="G15" t="n">
         <v>1.1208</v>
@@ -1624,13 +1624,13 @@
         <v>2.5224</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.1032</v>
+        <v>-0.5759</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7145</v>
+        <v>-0.5143</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3887</v>
+        <v>-0.0617</v>
       </c>
       <c r="V15" t="n">
         <v>2.4477</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.1714</v>
+        <v>1.4439</v>
       </c>
       <c r="E16" t="n">
-        <v>2.2536</v>
+        <v>1.8532</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0822</v>
+        <v>-0.4093</v>
       </c>
       <c r="G16" t="n">
         <v>-0.4832</v>
@@ -1702,13 +1702,13 @@
         <v>1.7463</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6546</v>
+        <v>-0.07290000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1951</v>
+        <v>-0.2053</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4594</v>
+        <v>0.1324</v>
       </c>
       <c r="V16" t="n">
         <v>1.2239</v>
@@ -1735,10 +1735,10 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5169</v>
+        <v>0.617</v>
       </c>
       <c r="E17" t="n">
-        <v>3.3864</v>
+        <v>3.4865</v>
       </c>
       <c r="F17" t="n">
         <v>-2.8694</v>
@@ -1780,10 +1780,10 @@
         <v>1.7463</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5092</v>
+        <v>-0.4091</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4116</v>
+        <v>-0.3115</v>
       </c>
       <c r="U17" t="n">
         <v>-0.09760000000000001</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1345</v>
+        <v>-0.3683</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8836000000000001</v>
+        <v>-1.0838</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0181</v>
+        <v>0.7155</v>
       </c>
       <c r="G18" t="n">
         <v>1.191</v>
@@ -1858,13 +1858,13 @@
         <v>1.7463</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8241000000000001</v>
+        <v>0.3213</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3623</v>
+        <v>-0.5625</v>
       </c>
       <c r="U18" t="n">
-        <v>1.1864</v>
+        <v>0.8838</v>
       </c>
       <c r="V18" t="n">
         <v>1.2239</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9761</v>
+        <v>-0.7854</v>
       </c>
       <c r="E19" t="n">
         <v>-0.8871</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.089</v>
+        <v>0.1018</v>
       </c>
       <c r="G19" t="n">
         <v>-1.1157</v>
@@ -1936,13 +1936,13 @@
         <v>0.9702</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8306</v>
+        <v>-0.6399</v>
       </c>
       <c r="T19" t="n">
         <v>-0.424</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4067</v>
+        <v>-0.2159</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.602</v>
+        <v>-1.6748</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0999</v>
+        <v>-0.2</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.5021</v>
+        <v>-1.4748</v>
       </c>
       <c r="G20" t="n">
         <v>-1.003</v>
@@ -2014,13 +2014,13 @@
         <v>0.3881</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2369</v>
+        <v>0.164</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4856</v>
+        <v>0.3855</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2488</v>
+        <v>-0.2215</v>
       </c>
       <c r="V20" t="n">
         <v>-1.2239</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. APARICIO IZQUIERDO</t>
+          <t>M. RODRÍGUEZ RIVEROL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.3332</v>
+        <v>-2.5596</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.8645</v>
+        <v>0.3378</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.4687</v>
+        <v>-2.8974</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.0888</v>
+        <v>-0.8346</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.5596</v>
+        <v>-0.2373</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.5292</v>
+        <v>-0.5973000000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.2093</v>
+        <v>0.4849</v>
       </c>
       <c r="K21" t="n">
-        <v>1.2976</v>
+        <v>1.071</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.5069</v>
+        <v>-0.5861</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.8795</v>
+        <v>-1.3195</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.8572</v>
+        <v>-1.3083</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.0223</v>
+        <v>-0.0111</v>
       </c>
       <c r="P21" t="n">
-        <v>1.7463</v>
+        <v>0.7761</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.7463</v>
+        <v>0.7761</v>
       </c>
       <c r="S21" t="n">
-        <v>0.9033</v>
+        <v>0.2765</v>
       </c>
       <c r="T21" t="n">
-        <v>0.06279999999999999</v>
+        <v>0.1828</v>
       </c>
       <c r="U21" t="n">
-        <v>0.8405</v>
+        <v>0.09370000000000001</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.894</v>
+        <v>-2.7776</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2821</v>
+        <v>-0.3299</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.1761</v>
+        <v>-2.4477</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.6968</v>
+        <v>-2.7701</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.1361</v>
+        <v>-2.5365</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.5607</v>
+        <v>-0.2336</v>
       </c>
       <c r="G22" t="n">
         <v>-2.3215</v>
@@ -2170,13 +2170,13 @@
         <v>0.9702</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3753</v>
+        <v>-0.4486</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0595</v>
+        <v>-0.4599</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3158</v>
+        <v>0.0112</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. RODRÍGUEZ RIVEROL</t>
+          <t>A. APARICIO IZQUIERDO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.8293</v>
+        <v>-2.9545</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3378</v>
+        <v>-1.2649</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.1671</v>
+        <v>-1.6896</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.8346</v>
+        <v>-4.0888</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.2373</v>
+        <v>-1.5596</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.5973000000000001</v>
+        <v>-2.5292</v>
       </c>
       <c r="J23" t="n">
-        <v>0.4849</v>
+        <v>-1.2093</v>
       </c>
       <c r="K23" t="n">
-        <v>1.071</v>
+        <v>1.2976</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.5861</v>
+        <v>-2.5069</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.3195</v>
+        <v>-2.8795</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.3083</v>
+        <v>-2.8572</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.0111</v>
+        <v>-0.0223</v>
       </c>
       <c r="P23" t="n">
-        <v>0.7761</v>
+        <v>1.7463</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.7761</v>
+        <v>1.7463</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0067</v>
+        <v>0.2821</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1828</v>
+        <v>-0.3376</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1761</v>
+        <v>0.6197</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.7776</v>
+        <v>-0.894</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.3299</v>
+        <v>0.2821</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.4477</v>
+        <v>-1.1761</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.0059</v>
+        <v>-4.199</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.1499</v>
+        <v>-3.4492</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.856</v>
+        <v>-0.7498</v>
       </c>
       <c r="G24" t="n">
         <v>-3.4521</v>
@@ -2326,13 +2326,13 @@
         <v>2.1344</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6732</v>
+        <v>0.1337</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.9567</v>
+        <v>-0.256</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2836</v>
+        <v>0.3898</v>
       </c>
       <c r="V24" t="n">
         <v>1.8358</v>
@@ -2359,19 +2359,19 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.214700000000001</v>
+        <v>-3.547499999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>7.056200000000001</v>
+        <v>7.056200000000002</v>
       </c>
       <c r="F25" t="n">
-        <v>-11.2708</v>
+        <v>-10.6034</v>
       </c>
       <c r="G25" t="n">
         <v>-5.1214</v>
       </c>
       <c r="H25" t="n">
-        <v>-7.151199999999999</v>
+        <v>-7.1512</v>
       </c>
       <c r="I25" t="n">
         <v>2.0299</v>
@@ -2404,13 +2404,13 @@
         <v>17.463</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.1815</v>
+        <v>-1.5142</v>
       </c>
       <c r="T25" t="n">
-        <v>-3.1407</v>
+        <v>-3.140700000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>0.9589999999999999</v>
+        <v>1.6265</v>
       </c>
       <c r="V25" t="n">
         <v>2.1178</v>
@@ -2419,7 +2419,7 @@
         <v>11.4835</v>
       </c>
       <c r="X25" t="n">
-        <v>-9.365500000000001</v>
+        <v>-9.365499999999999</v>
       </c>
     </row>
   </sheetData>
